--- a/applications/METFORMIN-HIIE_study/negative/neg_lipid_reference_set.xlsx
+++ b/applications/METFORMIN-HIIE_study/negative/neg_lipid_reference_set.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/negative/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/METFORMIN-HIIE_study/negative/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC10E61A-1641-984F-A5D5-16DC3B6146F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DADC9A7-B337-994A-8EDB-6A1CC642981E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17000" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>PC</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Palmitic acid-d31</t>
   </si>
   <si>
-    <t>Light</t>
-  </si>
-  <si>
     <t>LPI_1</t>
   </si>
   <si>
@@ -177,6 +174,12 @@
   </si>
   <si>
     <t>PC_2</t>
+  </si>
+  <si>
+    <t>LightSplash</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
 </sst>
 </file>
@@ -651,7 +654,7 @@
         <v>98.399999999999991</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -714,7 +717,7 @@
         <v>206.4</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -756,7 +759,7 @@
         <v>447.6</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -777,7 +780,7 @@
         <v>474.6</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -861,7 +864,7 @@
         <v>600.6</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -908,7 +911,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>22</v>
@@ -924,12 +927,12 @@
         <v>153.6</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>29</v>
@@ -945,12 +948,12 @@
         <v>165.6</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>30</v>
@@ -966,12 +969,12 @@
         <v>172.20000000000002</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -987,12 +990,12 @@
         <v>161.4</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>32</v>
@@ -1008,12 +1011,12 @@
         <v>457.2</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>33</v>
@@ -1029,7 +1032,7 @@
         <v>211.2</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
